--- a/survey_templates/048_student_motivation_survey--survey_templates.xlsx
+++ b/survey_templates/048_student_motivation_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -803,8 +803,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -832,12 +832,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'option1':_'i_am_motivated_by_a_sense_of_purpose_and_meaning'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'option1': 'I am motivated by a sense of purpose and meaning'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -849,12 +849,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'option2':_'i_am_motivated_by_a_desire_for_financial_gain'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'option2': 'I am motivated by a desire for financial gain'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -866,12 +866,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'option3':_'i_am_motivated_by_a_desire_for_personal_growth_and_development'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'option3': 'I am motivated by a desire for personal growth and development'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -883,12 +883,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'option4':_'i_am_motivated_by_a_desire_for_social_recognition'}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'option4': 'I am motivated by a desire for social recognition'}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -900,12 +900,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'option5':_'i_am_motivated_by_a_desire_for_fun'}</t>
+          <t>option_5</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'option5': 'I am motivated by a desire for fun'}</t>
+          <t>Option 5</t>
         </is>
       </c>
     </row>
@@ -917,12 +917,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'option1':_'leadership_skills'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'option1': 'Leadership skills'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -934,12 +934,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'option2':_'creativity_skills'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'option2': 'Creativity skills'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -951,12 +951,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'option3':_'analytical_skills'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'option3': 'Analytical skills'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -968,12 +968,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'option4':_'problem-solving_skills'}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'option4': 'Problem-solving skills'}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -985,12 +985,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'option5':_'communication_skills'}</t>
+          <t>option_5</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'option5': 'Communication skills'}</t>
+          <t>Option 5</t>
         </is>
       </c>
     </row>
@@ -1002,12 +1002,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'option1':_'procrastination'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'option1': 'Procrastination'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1019,12 +1019,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'option2':_'distractions'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'option2': 'Distractions'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1036,12 +1036,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'option3':_'self-doubt'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'option3': 'Self-doubt'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1053,12 +1053,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'option4':_'time-management'}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'option4': 'Time-management'}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'option5':_'lack_of_focus'}</t>
+          <t>option_5</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'option5': 'Lack of focus'}</t>
+          <t>Option 5</t>
         </is>
       </c>
     </row>
@@ -1087,12 +1087,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'option1':_'guidance'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'option1': 'Guidance'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1104,12 +1104,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'option2':_'support'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'option2': 'Support'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1121,12 +1121,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'option3':_'resources'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'option3': 'Resources'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1138,12 +1138,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'option4':_'feedback'}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'option4': 'Feedback'}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -1155,12 +1155,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'option5':_'recognition'}</t>
+          <t>option_5</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'option5': 'Recognition'}</t>
+          <t>Option 5</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1172,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'option1':_'yes,_i_am_working_towards_a_specific_goal'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'option1': 'Yes, I am working towards a specific goal'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'option2':_'no,_i_do_not_have_a_goal'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'option2': 'No, I do not have a goal'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1206,12 +1206,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'option1':_'lack_of_motivation'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'option1': 'Lack of motivation'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1223,12 +1223,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'option2':_'limited_resources'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'option2': 'Limited resources'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1240,12 +1240,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'option3':_'lack_of_time'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'option3': 'Lack of time'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1257,12 +1257,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'option4':_'external_factors'}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'option4': 'External factors'}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -1274,12 +1274,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'option5':_'internal_factors'}</t>
+          <t>option_5</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'option5': 'Internal factors'}</t>
+          <t>Option 5</t>
         </is>
       </c>
     </row>
@@ -1291,12 +1291,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'option1':_'develop_a_plan'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'option1': 'Develop a plan'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1308,12 +1308,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'option2':_'seek_help_and_support'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'option2': 'Seek help and support'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1325,12 +1325,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'option3':_'change_my_behavior'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'option3': 'Change my behavior'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1342,12 +1342,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'option4':_'practice_self-reflection'}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'option4': 'Practice self-reflection'}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -1359,12 +1359,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'option5':_'seek_out_new_opportunities'}</t>
+          <t>option_5</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'option5': 'Seek out new opportunities'}</t>
+          <t>Option 5</t>
         </is>
       </c>
     </row>
@@ -1376,12 +1376,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'option1':_'yes,_i_have_a_clear_plan'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'option1': 'Yes, I have a clear plan'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1393,12 +1393,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'option2':_'no,_i_do_not_have_a_plan'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'option2': 'No, I do not have a plan'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1410,12 +1410,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'option1':_'teacher'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'option1': 'Teacher'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1427,12 +1427,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'option2':_'parent'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'option2': 'Parent'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1444,12 +1444,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'option3':_'peer'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'option3': 'Peer'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1461,12 +1461,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'option4':_'counselor'}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'option4': 'Counselor'}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -1478,12 +1478,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'option5':_'self'}</t>
+          <t>option_5</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'option5': 'Self'}</t>
+          <t>Option 5</t>
         </is>
       </c>
     </row>
@@ -1495,12 +1495,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'option1':_'re-evaluate_my_goals'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'option1': 'Re-evaluate my goals'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1512,12 +1512,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'option2':_'seek_help_and_support'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'option2': 'Seek help and support'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{'option3':_'change_my_approach'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'option3': 'Change my approach'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1546,12 +1546,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>{'option4':_'set_a_new_goal'}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{'option4': 'Set a new goal'}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -1563,12 +1563,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>{'option5':_'give_up_on_the_goal'}</t>
+          <t>option_5</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{'option5': 'Give up on the goal'}</t>
+          <t>Option 5</t>
         </is>
       </c>
     </row>
